--- a/data/trans_dic/IP2001-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen caries</t>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 15,8</t>
+          <t>3,05; 16,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 14,86</t>
+          <t>3,37; 14,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 24,6</t>
+          <t>8,83; 25,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,09</t>
+          <t>0,88; 7,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 15,17</t>
+          <t>3,63; 16,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 24,4</t>
+          <t>8,41; 23,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 20,52</t>
+          <t>6,16; 21,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,2</t>
+          <t>4,71; 13,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 17,43</t>
+          <t>7,14; 16,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 20,3</t>
+          <t>9,67; 20,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,89</t>
+          <t>0,9; 5,38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 18,91</t>
+          <t>6,95; 18,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 22,52</t>
+          <t>9,07; 20,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,55</t>
+          <t>4,49; 13,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,39</t>
+          <t>0,34; 4,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,91; 24,4</t>
+          <t>12,46; 24,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 19,23</t>
+          <t>7,52; 19,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 13,11</t>
+          <t>3,86; 12,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 13,64</t>
+          <t>3,46; 13,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 19,76</t>
+          <t>11,48; 19,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 17,7</t>
+          <t>9,95; 18,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 11,58</t>
+          <t>5,21; 11,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,13</t>
+          <t>2,33; 8,32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 14,76</t>
+          <t>3,4; 15,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 11,34</t>
+          <t>1,24; 11,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 15,72</t>
+          <t>4,04; 16,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,59</t>
+          <t>0,93; 7,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 12,33</t>
+          <t>1,56; 11,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 17,61</t>
+          <t>3,63; 19,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,34</t>
+          <t>0,97; 5,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,6</t>
+          <t>3,38; 10,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,99</t>
+          <t>1,17; 7,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,7</t>
+          <t>4,74; 14,37</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,38</t>
+          <t>2,14; 10,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 18,25</t>
+          <t>6,3; 18,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,26; 27,44</t>
+          <t>12,39; 27,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 11,01</t>
+          <t>1,28; 11,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,15</t>
+          <t>1,07; 9,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 18,12</t>
+          <t>5,79; 17,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 26,84</t>
+          <t>11,83; 27,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,07</t>
+          <t>0,29; 14,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,75</t>
+          <t>2,35; 7,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 16,87</t>
+          <t>7,31; 16,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,83; 24,78</t>
+          <t>13,87; 24,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,87</t>
+          <t>2,1; 9,6</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,49; 34,35</t>
+          <t>12,71; 34,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 34,84</t>
+          <t>12,33; 35,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 21,3</t>
+          <t>5,02; 22,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 14,22</t>
+          <t>2,47; 14,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 18,9</t>
+          <t>4,96; 20,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 20,27</t>
+          <t>4,96; 21,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 29,62</t>
+          <t>10,16; 28,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 23,93</t>
+          <t>7,31; 23,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,26; 23,62</t>
+          <t>10,21; 23,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 25,13</t>
+          <t>10,5; 24,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 21,95</t>
+          <t>9,51; 21,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 16,96</t>
+          <t>5,76; 16,47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,31</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 14,54</t>
+          <t>2,46; 15,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,9; 16,89</t>
+          <t>2,93; 16,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,25</t>
+          <t>1,44; 12,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 25,37</t>
+          <t>7,91; 25,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 9,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,77</t>
+          <t>0,56; 5,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 17,85</t>
+          <t>6,87; 17,28</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,93</t>
+          <t>2,14; 10,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,92</t>
+          <t>1,32; 7,87</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,57</t>
+          <t>1,74; 8,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,63</t>
+          <t>2,79; 10,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 8,83</t>
+          <t>2,58; 9,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 12,13</t>
+          <t>4,1; 11,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,93</t>
+          <t>3,13; 10,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,74</t>
+          <t>4,39; 12,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 11,92</t>
+          <t>3,87; 11,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 15,93</t>
+          <t>6,27; 16,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,97</t>
+          <t>3,03; 7,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 10,14</t>
+          <t>4,49; 10,16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,98</t>
+          <t>4,11; 9,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,85</t>
+          <t>6,27; 12,96</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,05</t>
+          <t>8,29; 17,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 10,97</t>
+          <t>4,38; 11,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,26; 17,27</t>
+          <t>9,05; 17,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,0</t>
+          <t>0,6; 5,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,77; 13,17</t>
+          <t>5,85; 13,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,88</t>
+          <t>3,12; 8,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,59</t>
+          <t>7,9; 16,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,31</t>
+          <t>0,38; 4,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,02; 13,7</t>
+          <t>8,25; 13,79</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,83</t>
+          <t>4,5; 8,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,62; 15,27</t>
+          <t>9,4; 15,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,59</t>
+          <t>0,56; 3,48</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,33</t>
+          <t>6,72; 10,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,02</t>
+          <t>7,74; 11,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,58</t>
+          <t>8,71; 12,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,78</t>
+          <t>3,14; 5,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,72</t>
+          <t>6,46; 9,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,4</t>
+          <t>7,65; 11,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,71</t>
+          <t>7,95; 11,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,86</t>
+          <t>4,47; 7,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,44</t>
+          <t>7,1; 9,45</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,13; 10,79</t>
+          <t>8,03; 10,87</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,57</t>
+          <t>8,85; 11,47</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,48</t>
+          <t>4,19; 6,39</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4140</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9080</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2249</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9028</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7371</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8098</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13168</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16451</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1410; 7718</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1819; 7905</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4953; 14075</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>643; 5537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1932; 8719</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5109; 14499</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3756; 13037</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4550</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4685; 13305</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8191; 19477</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11322; 23440</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1353; 8057</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11676</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13593</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7953</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2685</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18951</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12583</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8640</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8676</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>30627</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>26177</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>16593</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>11360</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6590; 17376</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8706; 19727</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4446; 13222</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>422; 6118</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13063; 25393</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7572; 19330</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4136; 13783</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4318; 17198</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>22913; 38579</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>19556; 35471</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>10748; 24093</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5842; 20816</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4590</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2583</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1875</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7939</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4056</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10230</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4845</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2134; 9933</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>760; 6975</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2265; 9070</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>607; 4990</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1037; 7908</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5153</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2379; 12528</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1251; 7133</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4372; 13819</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1488; 9485</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5764; 17471</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3519</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8266</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14247</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14126</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3928</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6557</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16572</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>28373</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>7207</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1514; 7417</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4521; 13515</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9017; 19947</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>887; 7776</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>817; 7032</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4496; 13877</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9124; 21355</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>214; 11062</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3448; 11748</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>10924; 24435</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>20787; 37337</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3012; 13743</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8779</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4728</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4217</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7644</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5687</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>12996</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14286</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12371</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5071; 13652</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5160; 14702</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2055; 9117</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>844; 5114</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2052; 8455</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2245; 9585</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4325; 12234</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2977; 9709</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>8299; 19073</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>9143; 21362</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7941; 18160</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4312; 12338</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3169</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4317</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8345</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>11514</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5107</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3516</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4611</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1188; 7272</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1466; 8065</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>631; 5545</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3424</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4340; 13789</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3990</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4923</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>620; 6037</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>7090; 17839</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2222; 10474</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1296; 7718</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5030</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8685</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>7366</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10131</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>9725</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>15874</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>12396</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>17240</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>16461</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>24559</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2141; 10032</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3538; 13219</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3352; 12210</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>5055; 14096</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3954; 12728</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5732; 16827</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5150; 15071</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>9702; 24989</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>7555; 18588</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>11549; 26158</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>10819; 24711</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>17436; 36017</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>18674</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>11407</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>19539</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2516</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>13718</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>9149</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18185</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2332</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>32392</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>20556</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>37725</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>4848</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>12406; 26092</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>6906; 17928</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>13476; 26233</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>780; 6736</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>8952; 20747</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>5146; 14539</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>12540; 25604</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>588; 7418</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>24947; 41727</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>14511; 28601</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>28918; 47037</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>1606; 9900</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>54177</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>61495</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>69182</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>28454</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>44758</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>108265</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>127453</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>137136</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>73212</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>43146; 66270</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>51020; 77399</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>57365; 83173</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>20541; 38987</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>43736; 67227</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>53595; 80425</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>55615; 82868</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>33339; 57334</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>93664; 124699</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>109273; 147774</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>120256; 155821</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>58646; 89442</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2001-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 16,67</t>
+          <t>3,69; 17,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 14,65</t>
+          <t>3,09; 16,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 25,08</t>
+          <t>8,92; 24,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,6</t>
+          <t>0,91; 9,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 16,38</t>
+          <t>2,85; 15,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 23,86</t>
+          <t>8,5; 24,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 21,37</t>
+          <t>6,04; 21,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,91</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 13,37</t>
+          <t>4,43; 13,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 16,98</t>
+          <t>7,27; 17,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,67; 20,01</t>
+          <t>9,14; 19,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,38</t>
+          <t>0,91; 5,51</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 18,33</t>
+          <t>7,25; 17,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 20,55</t>
+          <t>8,72; 20,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 13,35</t>
+          <t>4,26; 13,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,87</t>
+          <t>0,42; 5,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,46; 24,22</t>
+          <t>12,82; 24,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 19,21</t>
+          <t>8,27; 19,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 12,87</t>
+          <t>4,42; 13,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,8</t>
+          <t>3,15; 12,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 19,32</t>
+          <t>11,32; 19,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 18,04</t>
+          <t>9,62; 17,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 11,69</t>
+          <t>5,41; 11,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,32</t>
+          <t>2,26; 7,84</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 15,82</t>
+          <t>3,41; 15,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,41</t>
+          <t>1,24; 11,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 16,18</t>
+          <t>3,81; 15,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,64</t>
+          <t>0,93; 7,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 11,91</t>
+          <t>1,47; 13,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 7,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 19,11</t>
+          <t>3,4; 16,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,52</t>
+          <t>0,96; 5,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,69</t>
+          <t>3,02; 11,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,46</t>
+          <t>1,18; 6,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 14,37</t>
+          <t>4,68; 13,36</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 10,5</t>
+          <t>1,54; 10,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 18,82</t>
+          <t>6,39; 20,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 27,41</t>
+          <t>12,49; 28,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,23</t>
+          <t>1,15; 11,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,21</t>
+          <t>1,07; 9,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 17,87</t>
+          <t>5,59; 18,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 27,69</t>
+          <t>10,89; 26,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 14,97</t>
+          <t>1,13; 15,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,99</t>
+          <t>2,13; 7,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 16,35</t>
+          <t>7,39; 15,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,87; 24,91</t>
+          <t>14,02; 24,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,6</t>
+          <t>2,15; 10,45</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 34,21</t>
+          <t>11,64; 34,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,33; 35,12</t>
+          <t>12,35; 34,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 22,26</t>
+          <t>4,8; 21,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 14,95</t>
+          <t>2,26; 14,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 20,43</t>
+          <t>3,48; 20,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 21,19</t>
+          <t>4,8; 21,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 28,73</t>
+          <t>10,27; 29,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 23,84</t>
+          <t>6,65; 23,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 23,47</t>
+          <t>9,9; 24,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 24,53</t>
+          <t>10,2; 24,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,51; 21,74</t>
+          <t>9,3; 21,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,76; 16,47</t>
+          <t>6,1; 16,44</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,64</t>
+          <t>0,0; 8,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,05</t>
+          <t>2,48; 14,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 16,1</t>
+          <t>3,89; 17,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,63</t>
+          <t>1,41; 12,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 5,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 25,12</t>
+          <t>8,22; 24,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,4</t>
+          <t>0,0; 7,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,09</t>
+          <t>0,0; 9,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,46</t>
+          <t>0,56; 4,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 17,28</t>
+          <t>7,04; 17,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 10,07</t>
+          <t>2,06; 9,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,87</t>
+          <t>1,33; 7,86</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,15</t>
+          <t>1,72; 8,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,42</t>
+          <t>2,72; 9,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 9,4</t>
+          <t>2,63; 9,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 11,45</t>
+          <t>3,94; 11,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 10,07</t>
+          <t>3,16; 10,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 12,89</t>
+          <t>4,56; 12,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 11,32</t>
+          <t>4,24; 11,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 16,14</t>
+          <t>6,23; 15,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,45</t>
+          <t>3,1; 7,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 10,16</t>
+          <t>4,24; 9,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,4</t>
+          <t>3,99; 9,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 12,96</t>
+          <t>6,03; 12,4</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,29; 17,44</t>
+          <t>8,85; 17,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,37</t>
+          <t>4,35; 11,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,05; 17,61</t>
+          <t>9,59; 18,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,21</t>
+          <t>0,6; 5,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,57</t>
+          <t>5,82; 13,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,83</t>
+          <t>3,22; 9,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,9; 16,12</t>
+          <t>7,79; 16,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,78</t>
+          <t>0,37; 4,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,25; 13,79</t>
+          <t>8,25; 14,12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,87</t>
+          <t>4,34; 8,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,4; 15,29</t>
+          <t>9,27; 15,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,48</t>
+          <t>0,64; 3,51</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,32</t>
+          <t>6,78; 10,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,74</t>
+          <t>7,47; 11,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,62</t>
+          <t>8,7; 12,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,96</t>
+          <t>3,09; 5,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,46; 9,92</t>
+          <t>6,4; 9,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,48</t>
+          <t>7,85; 11,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,84</t>
+          <t>7,93; 11,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,69</t>
+          <t>4,39; 7,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,1; 9,45</t>
+          <t>7,03; 9,42</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,87</t>
+          <t>8,25; 10,84</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,47</t>
+          <t>8,8; 11,32</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,39</t>
+          <t>4,22; 6,41</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1410; 7718</t>
+          <t>1710; 8030</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1819; 7905</t>
+          <t>1666; 8913</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4953; 14075</t>
+          <t>5007; 13993</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>643; 5537</t>
+          <t>665; 6579</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1932; 8719</t>
+          <t>1516; 8371</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5109; 14499</t>
+          <t>5169; 14885</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3756; 13037</t>
+          <t>3683; 12873</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4550</t>
+          <t>0; 4169</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4685; 13305</t>
+          <t>4408; 13544</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8191; 19477</t>
+          <t>8344; 19986</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11322; 23440</t>
+          <t>10706; 22780</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1353; 8057</t>
+          <t>1364; 8258</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6590; 17376</t>
+          <t>6875; 17054</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8706; 19727</t>
+          <t>8372; 19693</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4446; 13222</t>
+          <t>4216; 13557</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422; 6118</t>
+          <t>525; 6538</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13063; 25393</t>
+          <t>13442; 26087</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7572; 19330</t>
+          <t>8323; 19172</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4136; 13783</t>
+          <t>4736; 14149</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4318; 17198</t>
+          <t>3929; 15511</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22913; 38579</t>
+          <t>22594; 39431</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19556; 35471</t>
+          <t>18912; 35076</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10748; 24093</t>
+          <t>11150; 24311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5842; 20816</t>
+          <t>5649; 19627</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4845</t>
+          <t>0; 5337</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2134; 9933</t>
+          <t>2141; 9459</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>760; 6975</t>
+          <t>755; 7001</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2265; 9070</t>
+          <t>2136; 8640</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>607; 4990</t>
+          <t>608; 5003</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1037; 7908</t>
+          <t>976; 8814</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5153</t>
+          <t>0; 5180</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2379; 12528</t>
+          <t>2227; 10962</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1251; 7133</t>
+          <t>1238; 7022</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4372; 13819</t>
+          <t>3903; 14257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1488; 9485</t>
+          <t>1496; 8725</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5764; 17471</t>
+          <t>5695; 16254</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1514; 7417</t>
+          <t>1088; 7406</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4521; 13515</t>
+          <t>4592; 14456</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9017; 19947</t>
+          <t>9086; 20751</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887; 7776</t>
+          <t>797; 7827</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>817; 7032</t>
+          <t>814; 7161</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4496; 13877</t>
+          <t>4341; 14437</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9124; 21355</t>
+          <t>8400; 20411</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>214; 11062</t>
+          <t>834; 11327</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3448; 11748</t>
+          <t>3128; 11351</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10924; 24435</t>
+          <t>11041; 23777</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20787; 37337</t>
+          <t>21019; 36907</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3012; 13743</t>
+          <t>3084; 14954</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5071; 13652</t>
+          <t>4645; 13687</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5160; 14702</t>
+          <t>5170; 14398</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2055; 9117</t>
+          <t>1966; 8616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>844; 5114</t>
+          <t>773; 4987</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2052; 8455</t>
+          <t>1441; 8675</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2245; 9585</t>
+          <t>2174; 9903</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4325; 12234</t>
+          <t>4371; 12763</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2977; 9709</t>
+          <t>2709; 9738</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8299; 19073</t>
+          <t>8046; 19505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9143; 21362</t>
+          <t>8887; 21415</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7941; 18160</t>
+          <t>7765; 18194</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4312; 12338</t>
+          <t>4573; 12318</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4611</t>
+          <t>0; 4630</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1188; 7272</t>
+          <t>1199; 6891</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1466; 8065</t>
+          <t>1951; 8725</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>631; 5545</t>
+          <t>618; 5512</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3424</t>
+          <t>0; 3084</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4340; 13789</t>
+          <t>4510; 13612</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3990</t>
+          <t>0; 3943</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4923</t>
+          <t>0; 5340</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>620; 6037</t>
+          <t>615; 5186</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7090; 17839</t>
+          <t>7270; 17791</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2222; 10474</t>
+          <t>2143; 9546</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1296; 7718</t>
+          <t>1308; 7711</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2141; 10032</t>
+          <t>2124; 9899</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3538; 13219</t>
+          <t>3447; 12402</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3352; 12210</t>
+          <t>3409; 12216</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5055; 14096</t>
+          <t>4847; 14372</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3954; 12728</t>
+          <t>3992; 12817</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5732; 16827</t>
+          <t>5952; 16946</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5150; 15071</t>
+          <t>5643; 15805</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9702; 24989</t>
+          <t>9642; 24016</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7555; 18588</t>
+          <t>7737; 19054</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11549; 26158</t>
+          <t>10921; 23986</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10819; 24711</t>
+          <t>10486; 24497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17436; 36017</t>
+          <t>16774; 34483</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12406; 26092</t>
+          <t>13241; 25933</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6906; 17928</t>
+          <t>6864; 17477</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13476; 26233</t>
+          <t>14278; 27744</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>780; 6736</t>
+          <t>771; 6789</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8952; 20747</t>
+          <t>8894; 20289</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5146; 14539</t>
+          <t>5297; 14825</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12540; 25604</t>
+          <t>12370; 25582</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>588; 7418</t>
+          <t>581; 6883</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>24947; 41727</t>
+          <t>24957; 42710</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14511; 28601</t>
+          <t>13994; 28500</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28918; 47037</t>
+          <t>28535; 47144</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1606; 9900</t>
+          <t>1830; 9978</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>43146; 66270</t>
+          <t>43502; 66367</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>51020; 77399</t>
+          <t>49264; 74585</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57365; 83173</t>
+          <t>57351; 81317</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20541; 38987</t>
+          <t>20251; 38001</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>43736; 67227</t>
+          <t>43372; 66992</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53595; 80425</t>
+          <t>54990; 81579</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55615; 82868</t>
+          <t>55501; 82084</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>33339; 57334</t>
+          <t>32717; 57977</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>93664; 124699</t>
+          <t>92812; 124278</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109273; 147774</t>
+          <t>112165; 147484</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>120256; 155821</t>
+          <t>119580; 153733</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>58646; 89442</t>
+          <t>59127; 89761</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2001-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,19%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,68%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>16,18%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 17,34</t>
+          <t>3,0; 15,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 16,52</t>
+          <t>8,4; 24,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 24,93</t>
+          <t>5,73; 20,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,03</t>
+          <t>0,0; 5,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 15,73</t>
+          <t>3,13; 15,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 24,49</t>
+          <t>3,48; 14,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 21,1</t>
+          <t>9,79; 24,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>1,15; 9,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 13,61</t>
+          <t>4,21; 13,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 17,42</t>
+          <t>7,03; 17,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 19,45</t>
+          <t>9,54; 20,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,51</t>
+          <t>1,04; 5,54</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>12,31%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>14,16%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>8,03%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,07%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 17,99</t>
+          <t>12,91; 24,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 20,52</t>
+          <t>7,93; 19,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 13,69</t>
+          <t>4,39; 13,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,2</t>
+          <t>3,31; 14,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,82; 24,88</t>
+          <t>7,79; 18,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 19,05</t>
+          <t>9,52; 22,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 13,21</t>
+          <t>4,28; 13,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 12,44</t>
+          <t>0,7; 6,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 19,75</t>
+          <t>11,47; 19,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 17,84</t>
+          <t>9,52; 17,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,41; 11,79</t>
+          <t>5,26; 11,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,84</t>
+          <t>2,61; 8,43</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,14%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,31%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,23%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>0,93; 7,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 15,06</t>
+          <t>1,48; 12,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,45</t>
+          <t>0,0; 7,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 15,41</t>
+          <t>2,36; 15,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,66</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,27</t>
+          <t>3,38; 14,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,86</t>
+          <t>1,26; 11,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 16,72</t>
+          <t>3,9; 15,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,43</t>
+          <t>0,98; 5,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 11,03</t>
+          <t>3,32; 10,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,87</t>
+          <t>1,21; 6,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 13,36</t>
+          <t>4,15; 12,69</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,32%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,98%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11,51%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19,58%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,32%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 10,48</t>
+          <t>1,07; 9,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 20,13</t>
+          <t>5,86; 18,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 28,52</t>
+          <t>11,65; 26,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,31</t>
+          <t>1,44; 15,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,38</t>
+          <t>1,96; 10,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 18,59</t>
+          <t>5,96; 18,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 26,47</t>
+          <t>12,26; 27,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 15,33</t>
+          <t>1,26; 11,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 7,72</t>
+          <t>2,19; 7,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 15,91</t>
+          <t>7,32; 16,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,02; 24,62</t>
+          <t>13,83; 24,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,45</t>
+          <t>2,13; 10,22</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,19%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17,95%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14,34%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>22,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>22,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,54%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 34,3</t>
+          <t>3,44; 18,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,35; 34,4</t>
+          <t>4,67; 20,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 21,03</t>
+          <t>10,01; 29,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 14,58</t>
+          <t>6,87; 24,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 20,97</t>
+          <t>12,49; 34,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 21,89</t>
+          <t>12,6; 34,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,27; 29,97</t>
+          <t>4,81; 21,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 23,92</t>
+          <t>2,26; 14,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 24,0</t>
+          <t>10,26; 23,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 24,59</t>
+          <t>10,76; 25,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 21,78</t>
+          <t>9,18; 21,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,44</t>
+          <t>6,46; 17,07</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,56%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,26</t>
+          <t>7,87; 25,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 17,42</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,55</t>
+          <t>0,0; 8,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 8,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,22; 24,8</t>
+          <t>2,5; 14,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,31</t>
+          <t>2,9; 16,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,86</t>
+          <t>1,47; 12,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,69</t>
+          <t>0,56; 4,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,04; 17,24</t>
+          <t>6,77; 17,85</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,18</t>
+          <t>2,05; 8,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,86</t>
+          <t>0,78; 7,74</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,6%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,19%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,04</t>
+          <t>3,12; 9,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,78</t>
+          <t>4,18; 12,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,41</t>
+          <t>3,86; 11,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 11,67</t>
+          <t>7,05; 17,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,14</t>
+          <t>1,62; 7,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 12,98</t>
+          <t>2,66; 9,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 11,87</t>
+          <t>2,55; 8,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 15,51</t>
+          <t>4,17; 12,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,64</t>
+          <t>3,11; 7,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,32</t>
+          <t>4,34; 10,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,31</t>
+          <t>3,99; 8,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,4</t>
+          <t>6,58; 13,55</t>
         </is>
       </c>
     </row>
@@ -1629,44 +1629,44 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>12,48%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>7,24%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>13,12%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,45%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>10,71%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,85; 17,33</t>
+          <t>5,77; 13,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,09</t>
+          <t>2,91; 8,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,59; 18,63</t>
+          <t>7,97; 16,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,25</t>
+          <t>0,27; 3,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,82; 13,27</t>
+          <t>8,94; 18,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,0</t>
+          <t>4,47; 10,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,79; 16,11</t>
+          <t>9,26; 17,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,44</t>
+          <t>0,57; 6,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,25; 14,12</t>
+          <t>8,02; 13,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,84</t>
+          <t>4,4; 8,83</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,27; 15,32</t>
+          <t>9,62; 15,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,51</t>
+          <t>0,68; 3,51</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,34</t>
+          <t>6,51; 9,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,31</t>
+          <t>7,68; 11,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,34</t>
+          <t>7,9; 11,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,81</t>
+          <t>4,65; 8,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,89</t>
+          <t>6,75; 10,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,64</t>
+          <t>7,43; 11,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,73</t>
+          <t>8,53; 12,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,77</t>
+          <t>3,31; 6,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,03; 9,42</t>
+          <t>7,11; 9,44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,25; 10,84</t>
+          <t>8,13; 10,79</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,32</t>
+          <t>8,8; 11,57</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,41</t>
+          <t>4,42; 6,71</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2078,37 +2078,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9028</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7371</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3794</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4140</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>9080</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2249</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4304</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9028</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7371</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3223</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1710; 8030</t>
+          <t>1598; 8073</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1666; 8913</t>
+          <t>5106; 14827</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5007; 13993</t>
+          <t>3493; 12515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>665; 6579</t>
+          <t>0; 3658</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1516; 8371</t>
+          <t>1448; 7319</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5169; 14885</t>
+          <t>1876; 8014</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3683; 12873</t>
+          <t>5493; 13806</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4169</t>
+          <t>646; 5201</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4408; 13544</t>
+          <t>4188; 13140</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8344; 19986</t>
+          <t>8062; 19993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10706; 22780</t>
+          <t>11173; 23777</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1364; 8258</t>
+          <t>1233; 6562</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18951</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12583</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8640</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8129</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11676</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13593</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7953</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2685</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18951</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12583</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8640</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>10692</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6875; 17054</t>
+          <t>13538; 25578</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8372; 19693</t>
+          <t>7984; 19357</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4216; 13557</t>
+          <t>4702; 14043</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>525; 6538</t>
+          <t>3758; 15939</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13442; 26087</t>
+          <t>7391; 17925</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8323; 19172</t>
+          <t>9135; 21609</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4736; 14149</t>
+          <t>4240; 13419</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3929; 15511</t>
+          <t>696; 6440</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22594; 39431</t>
+          <t>22899; 39456</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18912; 35076</t>
+          <t>18728; 34798</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11150; 24311</t>
+          <t>10833; 23868</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5649; 19627</t>
+          <t>5568; 17966</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1875</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4253</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1369</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4590</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2583</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4673</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3349</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>8828</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5337</t>
+          <t>608; 4956</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2141; 9459</t>
+          <t>982; 8189</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>755; 7001</t>
+          <t>0; 5109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2136; 8640</t>
+          <t>1368; 8773</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>608; 5003</t>
+          <t>0; 4764</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>976; 8814</t>
+          <t>2120; 9272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5180</t>
+          <t>773; 6929</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2227; 10962</t>
+          <t>2133; 8511</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1238; 7022</t>
+          <t>1266; 6904</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3903; 14257</t>
+          <t>4287; 13702</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1496; 8725</t>
+          <t>1543; 8882</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5695; 16254</t>
+          <t>4677; 14302</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14126</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3869</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3519</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8266</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>14247</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3278</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8305</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14126</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7267</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1088; 7406</t>
+          <t>814; 6988</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4592; 14456</t>
+          <t>4549; 14066</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9086; 20751</t>
+          <t>8987; 20697</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>797; 7827</t>
+          <t>983; 10620</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>814; 7161</t>
+          <t>1383; 7334</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4341; 14437</t>
+          <t>4283; 13107</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8400; 20411</t>
+          <t>8923; 19968</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>834; 11327</t>
+          <t>882; 7900</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3128; 11351</t>
+          <t>3222; 11399</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11041; 23777</t>
+          <t>10940; 25211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21019; 36907</t>
+          <t>20725; 37135</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3084; 14954</t>
+          <t>2943; 14149</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4217</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7644</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5676</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>8779</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9220</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4728</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4217</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5066</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7644</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8050</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4645; 13687</t>
+          <t>1423; 7822</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5170; 14398</t>
+          <t>2115; 9172</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1966; 8616</t>
+          <t>4261; 12613</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>773; 4987</t>
+          <t>2718; 9689</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1441; 8675</t>
+          <t>4985; 13707</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2174; 9903</t>
+          <t>5275; 14585</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4371; 12763</t>
+          <t>1971; 8725</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2709; 9738</t>
+          <t>801; 5138</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8046; 19505</t>
+          <t>8342; 19202</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8887; 21415</t>
+          <t>9372; 21892</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7765; 18194</t>
+          <t>7668; 18336</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4573; 12318</t>
+          <t>4842; 12790</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8345</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1336</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>3169</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>4317</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>8345</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3255</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4630</t>
+          <t>0; 3352</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1199; 6891</t>
+          <t>4322; 13925</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1951; 8725</t>
+          <t>0; 3912</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>618; 5512</t>
+          <t>0; 4197</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3084</t>
+          <t>0; 4438</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4510; 13612</t>
+          <t>1209; 7027</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3943</t>
+          <t>1454; 8460</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5340</t>
+          <t>652; 5343</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>615; 5186</t>
+          <t>620; 5274</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7270; 17791</t>
+          <t>6983; 18419</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2143; 9546</t>
+          <t>2130; 9292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1308; 7711</t>
+          <t>713; 7099</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>7366</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10131</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9725</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>16073</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>5030</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>7109</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>6735</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8685</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7366</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>10131</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9725</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>24941</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2124; 9899</t>
+          <t>3938; 12555</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3447; 12402</t>
+          <t>5457; 16631</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3409; 12216</t>
+          <t>5142; 15876</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4847; 14372</t>
+          <t>9904; 24328</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3992; 12817</t>
+          <t>1999; 9321</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5952; 16946</t>
+          <t>3371; 12218</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5643; 15805</t>
+          <t>3309; 11464</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9642; 24016</t>
+          <t>5035; 15349</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7737; 19054</t>
+          <t>7767; 19892</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10921; 23986</t>
+          <t>11164; 26104</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10486; 24497</t>
+          <t>10497; 23605</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16774; 34483</t>
+          <t>17182; 35403</t>
         </is>
       </c>
     </row>
@@ -3529,37 +3529,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>13718</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9149</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>18185</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2085</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>18674</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>11407</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>19539</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2516</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>13718</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>9149</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>18185</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4770</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13241; 25933</t>
+          <t>8820; 20141</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6864; 17477</t>
+          <t>4791; 14629</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14278; 27744</t>
+          <t>12649; 26349</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>771; 6789</t>
+          <t>424; 6053</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8894; 20289</t>
+          <t>13371; 27004</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5297; 14825</t>
+          <t>7047; 17293</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12370; 25582</t>
+          <t>13789; 25723</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>581; 6883</t>
+          <t>793; 8325</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>24957; 42710</t>
+          <t>24256; 41462</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13994; 28500</t>
+          <t>14183; 28446</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28535; 47144</t>
+          <t>29613; 47000</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1830; 9978</t>
+          <t>2012; 10404</t>
         </is>
       </c>
     </row>
@@ -3742,37 +3742,37 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>54177</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>61495</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>69182</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>28454</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>54087</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>65958</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>67954</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>71027</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>43502; 66367</t>
+          <t>44124; 65847</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>49264; 74585</t>
+          <t>53823; 79914</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57351; 81317</t>
+          <t>55272; 81936</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20251; 38001</t>
+          <t>31994; 56115</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>43372; 66992</t>
+          <t>43339; 66323</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>54990; 81579</t>
+          <t>48968; 72618</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55501; 82084</t>
+          <t>56179; 82855</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>32717; 57977</t>
+          <t>20523; 37760</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>92812; 124278</t>
+          <t>93753; 124607</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>112165; 147484</t>
+          <t>110538; 146710</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>119580; 153733</t>
+          <t>119570; 157149</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>59127; 89761</t>
+          <t>57801; 87760</t>
         </is>
       </c>
     </row>
